--- a/Travel America/la-nyc-components-by-route.xlsx
+++ b/Travel America/la-nyc-components-by-route.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Angeles" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New York City" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NYC vs LA Delta" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Los Angeles'!$A$4:$E$139</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +63,35 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00805000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -95,8 +123,38 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -118,11 +176,25 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,6 +227,42 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6295,4 +6403,304 @@
   <autoFilter ref="A4:E133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>NYC vs LA Component Delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Green = route/component parity ✓   |   Amber = in LA only (LA ahead)   |   Red = in NYC only   |   City-specific equivalents (SoloNycQa↔SoloLaQa, SubwayBasics↔MetroBasics) treated as matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>NYC Route</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>LA Equivalent</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Import Path</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>ROUTES IN NYC BUT NOT IN LA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>None — every NYC route has an LA equivalent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>COMPONENTS IN NYC BUT NOT IN EQUIVALENT LA ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>None — all NYC components have LA equivalents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>ROUTES IN LA BUT NOT IN NYC  (LA is ahead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>/la/itinerary</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/header/header</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>LA only route</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr"/>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>LA only route</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr"/>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>@/app/components/Header/Footer/footer</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>LA only route</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>COMPONENTS IN LA BUT NOT IN EQUIVALENT NYC ROUTE  (LA is ahead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>/nyc/is-nyc-safe-at-night</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>/la/is-la-safe-at-night</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>In LA, missing in NYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>/nyc/neighborhood-guide</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>/la/neighborhood-guide</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>In LA, missing in NYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>/nyc/neighborhood-guide</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr"/>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/faqsection/faqsection</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>In LA, missing in NYC</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>